--- a/www/flightdata/xlsx/eoss-394.xlsx
+++ b/www/flightdata/xlsx/eoss-394.xlsx
@@ -2949,7 +2949,7 @@
         <v>46124.2933225463</v>
       </c>
       <c r="D2" s="1">
-        <v>46124.543287037035</v>
+        <v>46124.293287037035</v>
       </c>
       <c r="E2">
         <v>5216</v>
@@ -3056,7 +3056,7 @@
         <v>46124.293415416665</v>
       </c>
       <c r="D3" s="1">
-        <v>46124.54336805556</v>
+        <v>46124.29336805556</v>
       </c>
       <c r="E3">
         <v>5236</v>
@@ -3187,7 +3187,7 @@
         <v>46124.293691377316</v>
       </c>
       <c r="D4" s="1">
-        <v>46124.54363425926</v>
+        <v>46124.29363425926</v>
       </c>
       <c r="E4">
         <v>5685</v>
@@ -3330,7 +3330,7 @@
         <v>46124.29373240741</v>
       </c>
       <c r="D5" s="1">
-        <v>46124.54371527778</v>
+        <v>46124.29371527778</v>
       </c>
       <c r="E5">
         <v>5868</v>
@@ -3473,7 +3473,7 @@
         <v>46124.29401020833</v>
       </c>
       <c r="D6" s="1">
-        <v>46124.54398148148</v>
+        <v>46124.29398148148</v>
       </c>
       <c r="E6">
         <v>6334</v>
@@ -3616,7 +3616,7 @@
         <v>46124.29410847222</v>
       </c>
       <c r="D7" s="1">
-        <v>46124.5440625</v>
+        <v>46124.2940625</v>
       </c>
       <c r="E7">
         <v>6498</v>
@@ -3759,7 +3759,7 @@
         <v>46124.29442761574</v>
       </c>
       <c r="D8" s="1">
-        <v>46124.54440972222</v>
+        <v>46124.29440972222</v>
       </c>
       <c r="E8">
         <v>7111</v>
@@ -3902,7 +3902,7 @@
         <v>46124.294705162036</v>
       </c>
       <c r="D9" s="1">
-        <v>46124.54467592593</v>
+        <v>46124.29467592593</v>
       </c>
       <c r="E9">
         <v>7587</v>
@@ -4045,7 +4045,7 @@
         <v>46124.29510373843</v>
       </c>
       <c r="D10" s="1">
-        <v>46124.545023148145</v>
+        <v>46124.295023148145</v>
       </c>
       <c r="E10">
         <v>8227</v>
@@ -4188,7 +4188,7 @@
         <v>46124.29512173611</v>
       </c>
       <c r="D11" s="1">
-        <v>46124.54510416667</v>
+        <v>46124.29510416667</v>
       </c>
       <c r="E11">
         <v>8400</v>
@@ -4331,7 +4331,7 @@
         <v>46124.295400625</v>
       </c>
       <c r="D12" s="1">
-        <v>46124.54537037037</v>
+        <v>46124.29537037037</v>
       </c>
       <c r="E12">
         <v>8890</v>
@@ -4474,7 +4474,7 @@
         <v>46124.295497824074</v>
       </c>
       <c r="D13" s="1">
-        <v>46124.54545138889</v>
+        <v>46124.29545138889</v>
       </c>
       <c r="E13">
         <v>9084</v>
@@ -4617,7 +4617,7 @@
         <v>46124.29577493056</v>
       </c>
       <c r="D14" s="1">
-        <v>46124.54571759259</v>
+        <v>46124.29571759259</v>
       </c>
       <c r="E14">
         <v>9578</v>
@@ -4760,7 +4760,7 @@
         <v>46124.295816273145</v>
       </c>
       <c r="D15" s="1">
-        <v>46124.545798611114</v>
+        <v>46124.295798611114</v>
       </c>
       <c r="E15">
         <v>9753</v>
@@ -4903,7 +4903,7 @@
         <v>46124.2960994213</v>
       </c>
       <c r="D16" s="1">
-        <v>46124.546064814815</v>
+        <v>46124.296064814815</v>
       </c>
       <c r="E16">
         <v>10271</v>
@@ -5046,7 +5046,7 @@
         <v>46124.29619231482</v>
       </c>
       <c r="D17" s="1">
-        <v>46124.54614583333</v>
+        <v>46124.29614583333</v>
       </c>
       <c r="E17">
         <v>10451</v>
@@ -5189,7 +5189,7 @@
         <v>46124.29649259259</v>
       </c>
       <c r="D18" s="1">
-        <v>46124.54641203704</v>
+        <v>46124.29641203704</v>
       </c>
       <c r="E18">
         <v>10985</v>
@@ -5332,7 +5332,7 @@
         <v>46124.2965253125</v>
       </c>
       <c r="D19" s="1">
-        <v>46124.54649305555</v>
+        <v>46124.29649305555</v>
       </c>
       <c r="E19">
         <v>11164</v>
@@ -5475,7 +5475,7 @@
         <v>46124.296800034725</v>
       </c>
       <c r="D20" s="1">
-        <v>46124.54675925926</v>
+        <v>46124.29675925926</v>
       </c>
       <c r="E20">
         <v>11683</v>
@@ -5618,7 +5618,7 @@
         <v>46124.29688731481</v>
       </c>
       <c r="D21" s="1">
-        <v>46124.54684027778</v>
+        <v>46124.29684027778</v>
       </c>
       <c r="E21">
         <v>11865</v>
@@ -5761,7 +5761,7 @@
         <v>46124.29718837963</v>
       </c>
       <c r="D22" s="1">
-        <v>46124.547106481485</v>
+        <v>46124.297106481485</v>
       </c>
       <c r="E22">
         <v>12385</v>
@@ -5904,7 +5904,7 @@
         <v>46124.29720454861</v>
       </c>
       <c r="D23" s="1">
-        <v>46124.5471875</v>
+        <v>46124.2971875</v>
       </c>
       <c r="E23">
         <v>12558</v>
@@ -6047,7 +6047,7 @@
         <v>46124.297489363424</v>
       </c>
       <c r="D24" s="1">
-        <v>46124.5474537037</v>
+        <v>46124.2974537037</v>
       </c>
       <c r="E24">
         <v>13078</v>
@@ -6190,7 +6190,7 @@
         <v>46124.29758085648</v>
       </c>
       <c r="D25" s="1">
-        <v>46124.547534722224</v>
+        <v>46124.297534722224</v>
       </c>
       <c r="E25">
         <v>13254</v>
@@ -6333,7 +6333,7 @@
         <v>46124.29788226852</v>
       </c>
       <c r="D26" s="1">
-        <v>46124.547800925924</v>
+        <v>46124.297800925924</v>
       </c>
       <c r="E26">
         <v>13759</v>
@@ -6476,7 +6476,7 @@
         <v>46124.297912002316</v>
       </c>
       <c r="D27" s="1">
-        <v>46124.54788194445</v>
+        <v>46124.29788194445</v>
       </c>
       <c r="E27">
         <v>13942</v>
@@ -6619,7 +6619,7 @@
         <v>46124.29818844907</v>
       </c>
       <c r="D28" s="1">
-        <v>46124.54814814815</v>
+        <v>46124.29814814815</v>
       </c>
       <c r="E28">
         <v>14483</v>
@@ -6762,7 +6762,7 @@
         <v>46124.298276643516</v>
       </c>
       <c r="D29" s="1">
-        <v>46124.54822916666</v>
+        <v>46124.29822916666</v>
       </c>
       <c r="E29">
         <v>14653</v>
@@ -6905,7 +6905,7 @@
         <v>46124.298576712965</v>
       </c>
       <c r="D30" s="1">
-        <v>46124.54849537037</v>
+        <v>46124.29849537037</v>
       </c>
       <c r="E30">
         <v>15151</v>
@@ -7048,7 +7048,7 @@
         <v>46124.29859539352</v>
       </c>
       <c r="D31" s="1">
-        <v>46124.54857638889</v>
+        <v>46124.29857638889</v>
       </c>
       <c r="E31">
         <v>15319</v>
@@ -7191,7 +7191,7 @@
         <v>46124.29888271991</v>
       </c>
       <c r="D32" s="1">
-        <v>46124.548842592594</v>
+        <v>46124.298842592594</v>
       </c>
       <c r="E32">
         <v>15792</v>
@@ -7334,7 +7334,7 @@
         <v>46124.29897038195</v>
       </c>
       <c r="D33" s="1">
-        <v>46124.54892361111</v>
+        <v>46124.29892361111</v>
       </c>
       <c r="E33">
         <v>15978</v>
@@ -7477,7 +7477,7 @@
         <v>46124.29924796296</v>
       </c>
       <c r="D34" s="1">
-        <v>46124.54918981482</v>
+        <v>46124.29918981482</v>
       </c>
       <c r="E34">
         <v>16489</v>
@@ -7620,7 +7620,7 @@
         <v>46124.29928950231</v>
       </c>
       <c r="D35" s="1">
-        <v>46124.54927083333</v>
+        <v>46124.29927083333</v>
       </c>
       <c r="E35">
         <v>16678</v>
@@ -7763,7 +7763,7 @@
         <v>46124.29957775463</v>
       </c>
       <c r="D36" s="1">
-        <v>46124.54953703703</v>
+        <v>46124.29953703703</v>
       </c>
       <c r="E36">
         <v>17169</v>
@@ -7906,7 +7906,7 @@
         <v>46124.29966517361</v>
       </c>
       <c r="D37" s="1">
-        <v>46124.54961805556</v>
+        <v>46124.29961805556</v>
       </c>
       <c r="E37">
         <v>17379</v>
@@ -8049,7 +8049,7 @@
         <v>46124.299965185186</v>
       </c>
       <c r="D38" s="1">
-        <v>46124.54988425926</v>
+        <v>46124.29988425926</v>
       </c>
       <c r="E38">
         <v>17915</v>
@@ -8192,7 +8192,7 @@
         <v>46124.30027225694</v>
       </c>
       <c r="D39" s="1">
-        <v>46124.55023148148</v>
+        <v>46124.30023148148</v>
       </c>
       <c r="E39">
         <v>18638</v>
@@ -8335,7 +8335,7 @@
         <v>46124.30035986111</v>
       </c>
       <c r="D40" s="1">
-        <v>46124.5503125</v>
+        <v>46124.3003125</v>
       </c>
       <c r="E40">
         <v>18823</v>
@@ -8478,7 +8478,7 @@
         <v>46124.30066744213</v>
       </c>
       <c r="D41" s="1">
-        <v>46124.550578703704</v>
+        <v>46124.300578703704</v>
       </c>
       <c r="E41">
         <v>19303</v>
@@ -8621,7 +8621,7 @@
         <v>46124.30067758102</v>
       </c>
       <c r="D42" s="1">
-        <v>46124.55065972222</v>
+        <v>46124.30065972222</v>
       </c>
       <c r="E42">
         <v>19483</v>
@@ -8764,7 +8764,7 @@
         <v>46124.300977708335</v>
       </c>
       <c r="D43" s="1">
-        <v>46124.55092592593</v>
+        <v>46124.30092592593</v>
       </c>
       <c r="E43">
         <v>19959</v>
@@ -8907,7 +8907,7 @@
         <v>46124.30105527778</v>
       </c>
       <c r="D44" s="1">
-        <v>46124.55100694444</v>
+        <v>46124.30100694444</v>
       </c>
       <c r="E44">
         <v>20130</v>
@@ -9050,7 +9050,7 @@
         <v>46124.30135408565</v>
       </c>
       <c r="D45" s="1">
-        <v>46124.55127314815</v>
+        <v>46124.30127314815</v>
       </c>
       <c r="E45">
         <v>20656</v>
@@ -9193,7 +9193,7 @@
         <v>46124.30137246528</v>
       </c>
       <c r="D46" s="1">
-        <v>46124.551354166666</v>
+        <v>46124.301354166666</v>
       </c>
       <c r="E46">
         <v>20859</v>
@@ -9336,7 +9336,7 @@
         <v>46124.30165519676</v>
       </c>
       <c r="D47" s="1">
-        <v>46124.551620370374</v>
+        <v>46124.301620370374</v>
       </c>
       <c r="E47">
         <v>21337</v>
@@ -9479,7 +9479,7 @@
         <v>46124.301748645834</v>
       </c>
       <c r="D48" s="1">
-        <v>46124.55170138889</v>
+        <v>46124.30170138889</v>
       </c>
       <c r="E48">
         <v>21537</v>
@@ -9622,7 +9622,7 @@
         <v>46124.3020671875</v>
       </c>
       <c r="D49" s="1">
-        <v>46124.55204861111</v>
+        <v>46124.30204861111</v>
       </c>
       <c r="E49">
         <v>22215</v>
@@ -9765,7 +9765,7 @@
         <v>46124.30234393518</v>
       </c>
       <c r="D50" s="1">
-        <v>46124.55231481481</v>
+        <v>46124.30231481481</v>
       </c>
       <c r="E50">
         <v>22738</v>
@@ -9908,7 +9908,7 @@
         <v>46124.30244435185</v>
       </c>
       <c r="D51" s="1">
-        <v>46124.552395833336</v>
+        <v>46124.302395833336</v>
       </c>
       <c r="E51">
         <v>22908</v>
@@ -10051,7 +10051,7 @@
         <v>46124.302744155095</v>
       </c>
       <c r="D52" s="1">
-        <v>46124.55266203704</v>
+        <v>46124.30266203704</v>
       </c>
       <c r="E52">
         <v>23424</v>
@@ -10194,7 +10194,7 @@
         <v>46124.30276158565</v>
       </c>
       <c r="D53" s="1">
-        <v>46124.55274305555</v>
+        <v>46124.30274305555</v>
       </c>
       <c r="E53">
         <v>23597</v>
@@ -10337,7 +10337,7 @@
         <v>46124.30306828704</v>
       </c>
       <c r="D54" s="1">
-        <v>46124.55300925926</v>
+        <v>46124.30300925926</v>
       </c>
       <c r="E54">
         <v>24089</v>
@@ -10480,7 +10480,7 @@
         <v>46124.30313753472</v>
       </c>
       <c r="D55" s="1">
-        <v>46124.553090277775</v>
+        <v>46124.303090277775</v>
       </c>
       <c r="E55">
         <v>24270</v>
@@ -10623,7 +10623,7 @@
         <v>46124.30343774305</v>
       </c>
       <c r="D56" s="1">
-        <v>46124.55335648148</v>
+        <v>46124.30335648148</v>
       </c>
       <c r="E56">
         <v>24803</v>
@@ -10766,7 +10766,7 @@
         <v>46124.30345680556</v>
       </c>
       <c r="D57" s="1">
-        <v>46124.5534375</v>
+        <v>46124.3034375</v>
       </c>
       <c r="E57">
         <v>24975</v>
@@ -10909,7 +10909,7 @@
         <v>46124.30373357639</v>
       </c>
       <c r="D58" s="1">
-        <v>46124.55370370371</v>
+        <v>46124.30370370371</v>
       </c>
       <c r="E58">
         <v>25489</v>
@@ -11052,7 +11052,7 @@
         <v>46124.30383276621</v>
       </c>
       <c r="D59" s="1">
-        <v>46124.55378472222</v>
+        <v>46124.30378472222</v>
       </c>
       <c r="E59">
         <v>25670</v>
@@ -11195,7 +11195,7 @@
         <v>46124.304109247685</v>
       </c>
       <c r="D60" s="1">
-        <v>46124.55405092592</v>
+        <v>46124.30405092592</v>
       </c>
       <c r="E60">
         <v>26194</v>
@@ -11338,7 +11338,7 @@
         <v>46124.30415074074</v>
       </c>
       <c r="D61" s="1">
-        <v>46124.554131944446</v>
+        <v>46124.304131944446</v>
       </c>
       <c r="E61">
         <v>26366</v>
@@ -11481,7 +11481,7 @@
         <v>46124.30442905093</v>
       </c>
       <c r="D62" s="1">
-        <v>46124.554398148146</v>
+        <v>46124.304398148146</v>
       </c>
       <c r="E62">
         <v>26810</v>
@@ -11624,7 +11624,7 @@
         <v>46124.304542592596</v>
       </c>
       <c r="D63" s="1">
-        <v>46124.55447916667</v>
+        <v>46124.30447916667</v>
       </c>
       <c r="E63">
         <v>26992</v>
@@ -11767,7 +11767,7 @@
         <v>46124.30480511574</v>
       </c>
       <c r="D64" s="1">
-        <v>46124.55474537037</v>
+        <v>46124.30474537037</v>
       </c>
       <c r="E64">
         <v>27498</v>
@@ -11910,7 +11910,7 @@
         <v>46124.30484762732</v>
       </c>
       <c r="D65" s="1">
-        <v>46124.55482638889</v>
+        <v>46124.30482638889</v>
       </c>
       <c r="E65">
         <v>27655</v>
@@ -12053,7 +12053,7 @@
         <v>46124.305129189815</v>
       </c>
       <c r="D66" s="1">
-        <v>46124.55509259259</v>
+        <v>46124.30509259259</v>
       </c>
       <c r="E66">
         <v>28103</v>
@@ -12196,7 +12196,7 @@
         <v>46124.30522158565</v>
       </c>
       <c r="D67" s="1">
-        <v>46124.55517361111</v>
+        <v>46124.30517361111</v>
       </c>
       <c r="E67">
         <v>28252</v>
@@ -12339,7 +12339,7 @@
         <v>46124.30549856481</v>
       </c>
       <c r="D68" s="1">
-        <v>46124.555439814816</v>
+        <v>46124.305439814816</v>
       </c>
       <c r="E68">
         <v>28677</v>
@@ -12482,7 +12482,7 @@
         <v>46124.30553987269</v>
       </c>
       <c r="D69" s="1">
-        <v>46124.55552083333</v>
+        <v>46124.30552083333</v>
       </c>
       <c r="E69">
         <v>28824</v>
@@ -12625,7 +12625,7 @@
         <v>46124.30582424768</v>
       </c>
       <c r="D70" s="1">
-        <v>46124.55578703704</v>
+        <v>46124.30578703704</v>
       </c>
       <c r="E70">
         <v>29291</v>
@@ -12768,7 +12768,7 @@
         <v>46124.305916006946</v>
       </c>
       <c r="D71" s="1">
-        <v>46124.555868055555</v>
+        <v>46124.305868055555</v>
       </c>
       <c r="E71">
         <v>29449</v>
@@ -12911,7 +12911,7 @@
         <v>46124.306193819444</v>
       </c>
       <c r="D72" s="1">
-        <v>46124.55613425926</v>
+        <v>46124.30613425926</v>
       </c>
       <c r="E72">
         <v>29869</v>
@@ -13054,7 +13054,7 @@
         <v>46124.30623415509</v>
       </c>
       <c r="D73" s="1">
-        <v>46124.55621527778</v>
+        <v>46124.30621527778</v>
       </c>
       <c r="E73">
         <v>30056</v>
@@ -13197,7 +13197,7 @@
         <v>46124.3065171412</v>
       </c>
       <c r="D74" s="1">
-        <v>46124.55648148148</v>
+        <v>46124.30648148148</v>
       </c>
       <c r="E74">
         <v>30541</v>
@@ -13340,7 +13340,7 @@
         <v>46124.30661050926</v>
       </c>
       <c r="D75" s="1">
-        <v>46124.5565625</v>
+        <v>46124.3065625</v>
       </c>
       <c r="E75">
         <v>30674</v>
@@ -13483,7 +13483,7 @@
         <v>46124.30688819444</v>
       </c>
       <c r="D76" s="1">
-        <v>46124.5568287037</v>
+        <v>46124.3068287037</v>
       </c>
       <c r="E76">
         <v>31092</v>
@@ -13626,7 +13626,7 @@
         <v>46124.30693064815</v>
       </c>
       <c r="D77" s="1">
-        <v>46124.556909722225</v>
+        <v>46124.306909722225</v>
       </c>
       <c r="E77">
         <v>31250</v>
@@ -13769,7 +13769,7 @@
         <v>46124.30721195602</v>
       </c>
       <c r="D78" s="1">
-        <v>46124.557175925926</v>
+        <v>46124.307175925926</v>
       </c>
       <c r="E78">
         <v>31645</v>
@@ -13912,7 +13912,7 @@
         <v>46124.307305856484</v>
       </c>
       <c r="D79" s="1">
-        <v>46124.55725694444</v>
+        <v>46124.30725694444</v>
       </c>
       <c r="E79">
         <v>31804</v>
@@ -14055,7 +14055,7 @@
         <v>46124.30758105324</v>
       </c>
       <c r="D80" s="1">
-        <v>46124.55752314815</v>
+        <v>46124.30752314815</v>
       </c>
       <c r="E80">
         <v>32220</v>
@@ -14198,7 +14198,7 @@
         <v>46124.30762261574</v>
       </c>
       <c r="D81" s="1">
-        <v>46124.557604166665</v>
+        <v>46124.307604166665</v>
       </c>
       <c r="E81">
         <v>32373</v>
@@ -14341,7 +14341,7 @@
         <v>46124.30790599537</v>
       </c>
       <c r="D82" s="1">
-        <v>46124.55787037037</v>
+        <v>46124.30787037037</v>
       </c>
       <c r="E82">
         <v>32826</v>
@@ -14484,7 +14484,7 @@
         <v>46124.308014664355</v>
       </c>
       <c r="D83" s="1">
-        <v>46124.55795138889</v>
+        <v>46124.30795138889</v>
       </c>
       <c r="E83">
         <v>32992</v>
@@ -14627,7 +14627,7 @@
         <v>46124.30827670139</v>
       </c>
       <c r="D84" s="1">
-        <v>46124.558217592596</v>
+        <v>46124.308217592596</v>
       </c>
       <c r="E84">
         <v>33359</v>
@@ -14770,7 +14770,7 @@
         <v>46124.30832777778</v>
       </c>
       <c r="D85" s="1">
-        <v>46124.55829861111</v>
+        <v>46124.30829861111</v>
       </c>
       <c r="E85">
         <v>33549</v>
@@ -14913,7 +14913,7 @@
         <v>46124.30860042824</v>
       </c>
       <c r="D86" s="1">
-        <v>46124.55856481481</v>
+        <v>46124.30856481481</v>
       </c>
       <c r="E86">
         <v>34016</v>
@@ -15056,7 +15056,7 @@
         <v>46124.30869431713</v>
       </c>
       <c r="D87" s="1">
-        <v>46124.558645833335</v>
+        <v>46124.308645833335</v>
       </c>
       <c r="E87">
         <v>34209</v>
@@ -15199,7 +15199,7 @@
         <v>46124.30897041666</v>
       </c>
       <c r="D88" s="1">
-        <v>46124.558912037035</v>
+        <v>46124.308912037035</v>
       </c>
       <c r="E88">
         <v>34685</v>
@@ -15342,7 +15342,7 @@
         <v>46124.30901318287</v>
       </c>
       <c r="D89" s="1">
-        <v>46124.55899305556</v>
+        <v>46124.30899305556</v>
       </c>
       <c r="E89">
         <v>34893</v>
@@ -15485,7 +15485,7 @@
         <v>46124.30929510417</v>
       </c>
       <c r="D90" s="1">
-        <v>46124.55925925926</v>
+        <v>46124.30925925926</v>
       </c>
       <c r="E90">
         <v>35413</v>
@@ -15628,7 +15628,7 @@
         <v>46124.3093877662</v>
       </c>
       <c r="D91" s="1">
-        <v>46124.55934027778</v>
+        <v>46124.30934027778</v>
       </c>
       <c r="E91">
         <v>35582</v>
@@ -15771,7 +15771,7 @@
         <v>46124.30966490741</v>
       </c>
       <c r="D92" s="1">
-        <v>46124.55960648148</v>
+        <v>46124.30960648148</v>
       </c>
       <c r="E92">
         <v>36110</v>
@@ -15914,7 +15914,7 @@
         <v>46124.309707546294</v>
       </c>
       <c r="D93" s="1">
-        <v>46124.5596875</v>
+        <v>46124.3096875</v>
       </c>
       <c r="E93">
         <v>36278</v>
@@ -16057,7 +16057,7 @@
         <v>46124.30999582176</v>
       </c>
       <c r="D94" s="1">
-        <v>46124.559953703705</v>
+        <v>46124.309953703705</v>
       </c>
       <c r="E94">
         <v>36876</v>
@@ -16200,7 +16200,7 @@
         <v>46124.31013489583</v>
       </c>
       <c r="D95" s="1">
-        <v>46124.56003472222</v>
+        <v>46124.31003472222</v>
       </c>
       <c r="E95">
         <v>37074</v>
@@ -16343,7 +16343,7 @@
         <v>46124.31036105324</v>
       </c>
       <c r="D96" s="1">
-        <v>46124.56030092593</v>
+        <v>46124.31030092593</v>
       </c>
       <c r="E96">
         <v>37662</v>
@@ -16486,7 +16486,7 @@
         <v>46124.310412418985</v>
       </c>
       <c r="D97" s="1">
-        <v>46124.560381944444</v>
+        <v>46124.310381944444</v>
       </c>
       <c r="E97">
         <v>37851</v>
@@ -16629,7 +16629,7 @@
         <v>46124.31068407407</v>
       </c>
       <c r="D98" s="1">
-        <v>46124.560648148145</v>
+        <v>46124.310648148145</v>
       </c>
       <c r="E98">
         <v>38449</v>
@@ -16772,7 +16772,7 @@
         <v>46124.31076988426</v>
       </c>
       <c r="D99" s="1">
-        <v>46124.56072916667</v>
+        <v>46124.31072916667</v>
       </c>
       <c r="E99">
         <v>38627</v>
@@ -16915,7 +16915,7 @@
         <v>46124.31105476852</v>
       </c>
       <c r="D100" s="1">
-        <v>46124.56099537037</v>
+        <v>46124.31099537037</v>
       </c>
       <c r="E100">
         <v>39131</v>
@@ -17058,7 +17058,7 @@
         <v>46124.311095763886</v>
       </c>
       <c r="D101" s="1">
-        <v>46124.56107638889</v>
+        <v>46124.31107638889</v>
       </c>
       <c r="E101">
         <v>39306</v>
@@ -17201,7 +17201,7 @@
         <v>46124.31137847222</v>
       </c>
       <c r="D102" s="1">
-        <v>46124.56134259259</v>
+        <v>46124.31134259259</v>
       </c>
       <c r="E102">
         <v>39809</v>
@@ -17344,7 +17344,7 @@
         <v>46124.31147396991</v>
       </c>
       <c r="D103" s="1">
-        <v>46124.561423611114</v>
+        <v>46124.311423611114</v>
       </c>
       <c r="E103">
         <v>39994</v>
@@ -17487,7 +17487,7 @@
         <v>46124.31175030093</v>
       </c>
       <c r="D104" s="1">
-        <v>46124.561689814815</v>
+        <v>46124.311689814815</v>
       </c>
       <c r="E104">
         <v>40377</v>
@@ -17630,7 +17630,7 @@
         <v>46124.311786990744</v>
       </c>
       <c r="D105" s="1">
-        <v>46124.56177083333</v>
+        <v>46124.31177083333</v>
       </c>
       <c r="E105">
         <v>40573</v>
@@ -17773,7 +17773,7 @@
         <v>46124.31206701389</v>
       </c>
       <c r="D106" s="1">
-        <v>46124.56203703704</v>
+        <v>46124.31203703704</v>
       </c>
       <c r="E106">
         <v>41091</v>
@@ -17916,7 +17916,7 @@
         <v>46124.3121662037</v>
       </c>
       <c r="D107" s="1">
-        <v>46124.56211805555</v>
+        <v>46124.31211805555</v>
       </c>
       <c r="E107">
         <v>41275</v>
@@ -18059,7 +18059,7 @@
         <v>46124.31244550926</v>
       </c>
       <c r="D108" s="1">
-        <v>46124.56238425926</v>
+        <v>46124.31238425926</v>
       </c>
       <c r="E108">
         <v>41810</v>
@@ -18202,7 +18202,7 @@
         <v>46124.312488344905</v>
       </c>
       <c r="D109" s="1">
-        <v>46124.56246527778</v>
+        <v>46124.31246527778</v>
       </c>
       <c r="E109">
         <v>41952</v>
@@ -18348,7 +18348,7 @@
         <v>46124.31277236111</v>
       </c>
       <c r="D110" s="1">
-        <v>46124.562731481485</v>
+        <v>46124.312731481485</v>
       </c>
       <c r="E110">
         <v>42284</v>
@@ -18491,7 +18491,7 @@
         <v>46124.312868333334</v>
       </c>
       <c r="D111" s="1">
-        <v>46124.5628125</v>
+        <v>46124.3128125</v>
       </c>
       <c r="E111">
         <v>42412</v>
@@ -18634,7 +18634,7 @@
         <v>46124.31314092593</v>
       </c>
       <c r="D112" s="1">
-        <v>46124.5630787037</v>
+        <v>46124.3130787037</v>
       </c>
       <c r="E112">
         <v>42757</v>
@@ -18777,7 +18777,7 @@
         <v>46124.31318121528</v>
       </c>
       <c r="D113" s="1">
-        <v>46124.563159722224</v>
+        <v>46124.313159722224</v>
       </c>
       <c r="E113">
         <v>42923</v>
@@ -18920,7 +18920,7 @@
         <v>46124.31346125</v>
       </c>
       <c r="D114" s="1">
-        <v>46124.563425925924</v>
+        <v>46124.313425925924</v>
       </c>
       <c r="E114">
         <v>43279</v>
@@ -19063,7 +19063,7 @@
         <v>46124.31355164352</v>
       </c>
       <c r="D115" s="1">
-        <v>46124.56350694445</v>
+        <v>46124.31350694445</v>
       </c>
       <c r="E115">
         <v>43387</v>
@@ -19206,7 +19206,7 @@
         <v>46124.31383244213</v>
       </c>
       <c r="D116" s="1">
-        <v>46124.56377314815</v>
+        <v>46124.31377314815</v>
       </c>
       <c r="E116">
         <v>43725</v>
@@ -19349,7 +19349,7 @@
         <v>46124.314156747685</v>
       </c>
       <c r="D117" s="1">
-        <v>46124.56412037037</v>
+        <v>46124.31412037037</v>
       </c>
       <c r="E117">
         <v>44273</v>
@@ -19492,7 +19492,7 @@
         <v>46124.31424872685</v>
       </c>
       <c r="D118" s="1">
-        <v>46124.56420138889</v>
+        <v>46124.31420138889</v>
       </c>
       <c r="E118">
         <v>44402</v>
@@ -19635,7 +19635,7 @@
         <v>46124.314527222225</v>
       </c>
       <c r="D119" s="1">
-        <v>46124.564467592594</v>
+        <v>46124.314467592594</v>
       </c>
       <c r="E119">
         <v>44745</v>
@@ -19778,7 +19778,7 @@
         <v>46124.314568194444</v>
       </c>
       <c r="D120" s="1">
-        <v>46124.56454861111</v>
+        <v>46124.31454861111</v>
       </c>
       <c r="E120">
         <v>44892</v>
@@ -19921,7 +19921,7 @@
         <v>46124.31485099537</v>
       </c>
       <c r="D121" s="1">
-        <v>46124.56481481482</v>
+        <v>46124.31481481482</v>
       </c>
       <c r="E121">
         <v>45221</v>
@@ -20064,7 +20064,7 @@
         <v>46124.314941689816</v>
       </c>
       <c r="D122" s="1">
-        <v>46124.56489583333</v>
+        <v>46124.31489583333</v>
       </c>
       <c r="E122">
         <v>45351</v>
@@ -20207,7 +20207,7 @@
         <v>46124.31522434028</v>
       </c>
       <c r="D123" s="1">
-        <v>46124.56516203703</v>
+        <v>46124.31516203703</v>
       </c>
       <c r="E123">
         <v>45696</v>
@@ -20350,7 +20350,7 @@
         <v>46124.31526314815</v>
       </c>
       <c r="D124" s="1">
-        <v>46124.56524305556</v>
+        <v>46124.31524305556</v>
       </c>
       <c r="E124">
         <v>45833</v>
@@ -20493,7 +20493,7 @@
         <v>46124.31554575232</v>
       </c>
       <c r="D125" s="1">
-        <v>46124.56550925926</v>
+        <v>46124.31550925926</v>
       </c>
       <c r="E125">
         <v>46190</v>
@@ -20636,7 +20636,7 @@
         <v>46124.31564008102</v>
       </c>
       <c r="D126" s="1">
-        <v>46124.56559027778</v>
+        <v>46124.31559027778</v>
       </c>
       <c r="E126">
         <v>46316</v>
@@ -20779,7 +20779,7 @@
         <v>46124.31591991898</v>
       </c>
       <c r="D127" s="1">
-        <v>46124.56585648148</v>
+        <v>46124.31585648148</v>
       </c>
       <c r="E127">
         <v>46636</v>
@@ -20922,7 +20922,7 @@
         <v>46124.315958506944</v>
       </c>
       <c r="D128" s="1">
-        <v>46124.5659375</v>
+        <v>46124.3159375</v>
       </c>
       <c r="E128">
         <v>46779</v>
@@ -21065,7 +21065,7 @@
         <v>46124.316239768516</v>
       </c>
       <c r="D129" s="1">
-        <v>46124.566203703704</v>
+        <v>46124.316203703704</v>
       </c>
       <c r="E129">
         <v>47073</v>
@@ -21208,7 +21208,7 @@
         <v>46124.316615104166</v>
       </c>
       <c r="D130" s="1">
-        <v>46124.56655092593</v>
+        <v>46124.31655092593</v>
       </c>
       <c r="E130">
         <v>47532</v>
@@ -21351,7 +21351,7 @@
         <v>46124.31664962963</v>
       </c>
       <c r="D131" s="1">
-        <v>46124.56663194444</v>
+        <v>46124.31663194444</v>
       </c>
       <c r="E131">
         <v>47692</v>
@@ -21494,7 +21494,7 @@
         <v>46124.31694070602</v>
       </c>
       <c r="D132" s="1">
-        <v>46124.56689814815</v>
+        <v>46124.31689814815</v>
       </c>
       <c r="E132">
         <v>48079</v>
@@ -21637,7 +21637,7 @@
         <v>46124.31702877315</v>
       </c>
       <c r="D133" s="1">
-        <v>46124.566979166666</v>
+        <v>46124.316979166666</v>
       </c>
       <c r="E133">
         <v>48215</v>
@@ -21780,7 +21780,7 @@
         <v>46124.3173052662</v>
       </c>
       <c r="D134" s="1">
-        <v>46124.567245370374</v>
+        <v>46124.317245370374</v>
       </c>
       <c r="E134">
         <v>48530</v>
@@ -21923,7 +21923,7 @@
         <v>46124.31734111111</v>
       </c>
       <c r="D135" s="1">
-        <v>46124.56732638889</v>
+        <v>46124.31732638889</v>
       </c>
       <c r="E135">
         <v>48661</v>
@@ -22066,7 +22066,7 @@
         <v>46124.31762295139</v>
       </c>
       <c r="D136" s="1">
-        <v>46124.56759259259</v>
+        <v>46124.31759259259</v>
       </c>
       <c r="E136">
         <v>49177</v>
@@ -22209,7 +22209,7 @@
         <v>46124.31772103009</v>
       </c>
       <c r="D137" s="1">
-        <v>46124.56767361111</v>
+        <v>46124.31767361111</v>
       </c>
       <c r="E137">
         <v>49340</v>
@@ -22352,7 +22352,7 @@
         <v>46124.318004560184</v>
       </c>
       <c r="D138" s="1">
-        <v>46124.56793981481</v>
+        <v>46124.31793981481</v>
       </c>
       <c r="E138">
         <v>49622</v>
@@ -22495,7 +22495,7 @@
         <v>46124.318040266204</v>
       </c>
       <c r="D139" s="1">
-        <v>46124.568020833336</v>
+        <v>46124.318020833336</v>
       </c>
       <c r="E139">
         <v>49732</v>
@@ -22638,7 +22638,7 @@
         <v>46124.318328333335</v>
       </c>
       <c r="D140" s="1">
-        <v>46124.56828703704</v>
+        <v>46124.31828703704</v>
       </c>
       <c r="E140">
         <v>50024</v>
@@ -22781,7 +22781,7 @@
         <v>46124.31842729167</v>
       </c>
       <c r="D141" s="1">
-        <v>46124.56836805555</v>
+        <v>46124.31836805555</v>
       </c>
       <c r="E141">
         <v>50147</v>
@@ -22924,7 +22924,7 @@
         <v>46124.31869957176</v>
       </c>
       <c r="D142" s="1">
-        <v>46124.56863425926</v>
+        <v>46124.31863425926</v>
       </c>
       <c r="E142">
         <v>50437</v>
@@ -23067,7 +23067,7 @@
         <v>46124.318734409724</v>
       </c>
       <c r="D143" s="1">
-        <v>46124.568715277775</v>
+        <v>46124.318715277775</v>
       </c>
       <c r="E143">
         <v>50567</v>
@@ -23210,7 +23210,7 @@
         <v>46124.31901924768</v>
       </c>
       <c r="D144" s="1">
-        <v>46124.56898148148</v>
+        <v>46124.31898148148</v>
       </c>
       <c r="E144">
         <v>50853</v>
@@ -23353,7 +23353,7 @@
         <v>46124.3191234375</v>
       </c>
       <c r="D145" s="1">
-        <v>46124.5690625</v>
+        <v>46124.3190625</v>
       </c>
       <c r="E145">
         <v>51008</v>
@@ -23496,7 +23496,7 @@
         <v>46124.31943546296</v>
       </c>
       <c r="D146" s="1">
-        <v>46124.56940972222</v>
+        <v>46124.31940972222</v>
       </c>
       <c r="E146">
         <v>51445</v>
@@ -23639,7 +23639,7 @@
         <v>46124.31971256944</v>
       </c>
       <c r="D147" s="1">
-        <v>46124.56967592592</v>
+        <v>46124.31967592592</v>
       </c>
       <c r="E147">
         <v>51751</v>
@@ -23782,7 +23782,7 @@
         <v>46124.31981685185</v>
       </c>
       <c r="D148" s="1">
-        <v>46124.569756944446</v>
+        <v>46124.319756944446</v>
       </c>
       <c r="E148">
         <v>51884</v>
@@ -23925,7 +23925,7 @@
         <v>46124.32008914352</v>
       </c>
       <c r="D149" s="1">
-        <v>46124.570023148146</v>
+        <v>46124.320023148146</v>
       </c>
       <c r="E149">
         <v>52192</v>
@@ -24068,7 +24068,7 @@
         <v>46124.32012377315</v>
       </c>
       <c r="D150" s="1">
-        <v>46124.57010416667</v>
+        <v>46124.32010416667</v>
       </c>
       <c r="E150">
         <v>52315</v>
@@ -24211,7 +24211,7 @@
         <v>46124.32040105324</v>
       </c>
       <c r="D151" s="1">
-        <v>46124.57037037037</v>
+        <v>46124.32037037037</v>
       </c>
       <c r="E151">
         <v>52629</v>
@@ -24354,7 +24354,7 @@
         <v>46124.32050204861</v>
       </c>
       <c r="D152" s="1">
-        <v>46124.57045138889</v>
+        <v>46124.32045138889</v>
       </c>
       <c r="E152">
         <v>52762</v>
@@ -24497,7 +24497,7 @@
         <v>46124.320784791664</v>
       </c>
       <c r="D153" s="1">
-        <v>46124.57071759259</v>
+        <v>46124.32071759259</v>
       </c>
       <c r="E153">
         <v>53082</v>
@@ -24640,7 +24640,7 @@
         <v>46124.3208172338</v>
       </c>
       <c r="D154" s="1">
-        <v>46124.57079861111</v>
+        <v>46124.32079861111</v>
       </c>
       <c r="E154">
         <v>53219</v>
@@ -24783,7 +24783,7 @@
         <v>46124.32110666667</v>
       </c>
       <c r="D155" s="1">
-        <v>46124.571064814816</v>
+        <v>46124.321064814816</v>
       </c>
       <c r="E155">
         <v>53547</v>
@@ -24926,7 +24926,7 @@
         <v>46124.32119408565</v>
       </c>
       <c r="D156" s="1">
-        <v>46124.57114583333</v>
+        <v>46124.32114583333</v>
       </c>
       <c r="E156">
         <v>53685</v>
@@ -25069,7 +25069,7 @@
         <v>46124.32147739583</v>
       </c>
       <c r="D157" s="1">
-        <v>46124.57141203704</v>
+        <v>46124.32141203704</v>
       </c>
       <c r="E157">
         <v>54025</v>
@@ -25212,7 +25212,7 @@
         <v>46124.32151099537</v>
       </c>
       <c r="D158" s="1">
-        <v>46124.571493055555</v>
+        <v>46124.321493055555</v>
       </c>
       <c r="E158">
         <v>54162</v>
@@ -25355,7 +25355,7 @@
         <v>46124.32178993055</v>
       </c>
       <c r="D159" s="1">
-        <v>46124.57175925926</v>
+        <v>46124.32175925926</v>
       </c>
       <c r="E159">
         <v>54459</v>
@@ -25498,7 +25498,7 @@
         <v>46124.321890625</v>
       </c>
       <c r="D160" s="1">
-        <v>46124.57184027778</v>
+        <v>46124.32184027778</v>
       </c>
       <c r="E160">
         <v>54580</v>
@@ -25641,7 +25641,7 @@
         <v>46124.322170625</v>
       </c>
       <c r="D161" s="1">
-        <v>46124.57210648148</v>
+        <v>46124.32210648148</v>
       </c>
       <c r="E161">
         <v>54870</v>
@@ -25784,7 +25784,7 @@
         <v>46124.322215706015</v>
       </c>
       <c r="D162" s="1">
-        <v>46124.5721875</v>
+        <v>46124.3221875</v>
       </c>
       <c r="E162">
         <v>54733</v>
@@ -25927,7 +25927,7 @@
         <v>46124.32249559028</v>
       </c>
       <c r="D163" s="1">
-        <v>46124.5724537037</v>
+        <v>46124.3224537037</v>
       </c>
       <c r="E163">
         <v>55235</v>
@@ -26070,7 +26070,7 @@
         <v>46124.32258078704</v>
       </c>
       <c r="D164" s="1">
-        <v>46124.572534722225</v>
+        <v>46124.322534722225</v>
       </c>
       <c r="E164">
         <v>54733</v>
@@ -26213,7 +26213,7 @@
         <v>46124.32286219907</v>
       </c>
       <c r="D165" s="1">
-        <v>46124.572800925926</v>
+        <v>46124.322800925926</v>
       </c>
       <c r="E165">
         <v>55590</v>
@@ -26356,7 +26356,7 @@
         <v>46124.32290063657</v>
       </c>
       <c r="D166" s="1">
-        <v>46124.57288194444</v>
+        <v>46124.32288194444</v>
       </c>
       <c r="E166">
         <v>54733</v>
@@ -26499,7 +26499,7 @@
         <v>46124.32318480324</v>
       </c>
       <c r="D167" s="1">
-        <v>46124.57314814815</v>
+        <v>46124.32314814815</v>
       </c>
       <c r="E167">
         <v>55979</v>
@@ -26642,7 +26642,7 @@
         <v>46124.32328172454</v>
       </c>
       <c r="D168" s="1">
-        <v>46124.573229166665</v>
+        <v>46124.323229166665</v>
       </c>
       <c r="E168">
         <v>54733</v>
@@ -26785,7 +26785,7 @@
         <v>46124.32355796296</v>
       </c>
       <c r="D169" s="1">
-        <v>46124.57349537037</v>
+        <v>46124.32349537037</v>
       </c>
       <c r="E169">
         <v>56421</v>
@@ -26928,7 +26928,7 @@
         <v>46124.32359490741</v>
       </c>
       <c r="D170" s="1">
-        <v>46124.57357638889</v>
+        <v>46124.32357638889</v>
       </c>
       <c r="E170">
         <v>54733</v>
@@ -27071,7 +27071,7 @@
         <v>46124.32388038195</v>
       </c>
       <c r="D171" s="1">
-        <v>46124.573842592596</v>
+        <v>46124.323842592596</v>
       </c>
       <c r="E171">
         <v>56901</v>
@@ -27214,7 +27214,7 @@
         <v>46124.32401833333</v>
       </c>
       <c r="D172" s="1">
-        <v>46124.57392361111</v>
+        <v>46124.32392361111</v>
       </c>
       <c r="E172">
         <v>54733</v>
@@ -27357,7 +27357,7 @@
         <v>46124.32425039352</v>
       </c>
       <c r="D173" s="1">
-        <v>46124.57418981481</v>
+        <v>46124.32418981481</v>
       </c>
       <c r="E173">
         <v>57385</v>
@@ -27500,7 +27500,7 @@
         <v>46124.324295405095</v>
       </c>
       <c r="D174" s="1">
-        <v>46124.574270833335</v>
+        <v>46124.324270833335</v>
       </c>
       <c r="E174">
         <v>54733</v>
@@ -27643,7 +27643,7 @@
         <v>46124.32457664352</v>
       </c>
       <c r="D175" s="1">
-        <v>46124.574537037035</v>
+        <v>46124.324537037035</v>
       </c>
       <c r="E175">
         <v>57919</v>
@@ -27786,7 +27786,7 @@
         <v>46124.32470563657</v>
       </c>
       <c r="D176" s="1">
-        <v>46124.57461805556</v>
+        <v>46124.32461805556</v>
       </c>
       <c r="E176">
         <v>54733</v>
@@ -27932,7 +27932,7 @@
         <v>46124.32526805555</v>
       </c>
       <c r="D177" s="1">
-        <v>46124.57523148148</v>
+        <v>46124.32523148148</v>
       </c>
       <c r="E177">
         <v>58919</v>
@@ -28075,7 +28075,7 @@
         <v>46124.32596336806</v>
       </c>
       <c r="D178" s="1">
-        <v>46124.57592592593</v>
+        <v>46124.32592592593</v>
       </c>
       <c r="E178">
         <v>60051</v>
@@ -28218,7 +28218,7 @@
         <v>46124.3266584375</v>
       </c>
       <c r="D179" s="1">
-        <v>46124.57662037037</v>
+        <v>46124.32662037037</v>
       </c>
       <c r="E179">
         <v>61263</v>
@@ -28361,7 +28361,7 @@
         <v>46124.32734236111</v>
       </c>
       <c r="D180" s="1">
-        <v>46124.577314814815</v>
+        <v>46124.327314814815</v>
       </c>
       <c r="E180">
         <v>62552</v>
@@ -28504,7 +28504,7 @@
         <v>46124.32772059028</v>
       </c>
       <c r="D181" s="1">
-        <v>46124.57766203704</v>
+        <v>46124.32766203704</v>
       </c>
       <c r="E181">
         <v>63124</v>
@@ -28647,7 +28647,7 @@
         <v>46124.32804707176</v>
       </c>
       <c r="D182" s="1">
-        <v>46124.57800925926</v>
+        <v>46124.32800925926</v>
       </c>
       <c r="E182">
         <v>63730</v>
@@ -28790,7 +28790,7 @@
         <v>46124.32874186343</v>
       </c>
       <c r="D183" s="1">
-        <v>46124.5787037037</v>
+        <v>46124.3287037037</v>
       </c>
       <c r="E183">
         <v>64847</v>
@@ -28933,7 +28933,7 @@
         <v>46124.329436388885</v>
       </c>
       <c r="D184" s="1">
-        <v>46124.57939814815</v>
+        <v>46124.32939814815</v>
       </c>
       <c r="E184">
         <v>65816</v>
@@ -29076,7 +29076,7 @@
         <v>46124.33013028935</v>
       </c>
       <c r="D185" s="1">
-        <v>46124.580092592594</v>
+        <v>46124.330092592594</v>
       </c>
       <c r="E185">
         <v>66682</v>
@@ -29219,7 +29219,7 @@
         <v>46124.330825474535</v>
       </c>
       <c r="D186" s="1">
-        <v>46124.58078703703</v>
+        <v>46124.33078703703</v>
       </c>
       <c r="E186">
         <v>67621</v>
@@ -29362,7 +29362,7 @@
         <v>46124.33152049768</v>
       </c>
       <c r="D187" s="1">
-        <v>46124.58148148148</v>
+        <v>46124.33148148148</v>
       </c>
       <c r="E187">
         <v>69005</v>
@@ -29505,7 +29505,7 @@
         <v>46124.332203391205</v>
       </c>
       <c r="D188" s="1">
-        <v>46124.58217592593</v>
+        <v>46124.33217592593</v>
       </c>
       <c r="E188">
         <v>70457</v>
@@ -29648,7 +29648,7 @@
         <v>46124.33290930556</v>
       </c>
       <c r="D189" s="1">
-        <v>46124.582870370374</v>
+        <v>46124.332870370374</v>
       </c>
       <c r="E189">
         <v>71783</v>
@@ -29791,7 +29791,7 @@
         <v>46124.33360243055</v>
       </c>
       <c r="D190" s="1">
-        <v>46124.58356481481</v>
+        <v>46124.33356481481</v>
       </c>
       <c r="E190">
         <v>72818</v>
@@ -29934,7 +29934,7 @@
         <v>46124.334297719906</v>
       </c>
       <c r="D191" s="1">
-        <v>46124.58425925926</v>
+        <v>46124.33425925926</v>
       </c>
       <c r="E191">
         <v>73655</v>
@@ -30077,7 +30077,7 @@
         <v>46124.33467487268</v>
       </c>
       <c r="D192" s="1">
-        <v>46124.58460648148</v>
+        <v>46124.33460648148</v>
       </c>
       <c r="E192">
         <v>74065</v>
@@ -30220,7 +30220,7 @@
         <v>46124.3349924537</v>
       </c>
       <c r="D193" s="1">
-        <v>46124.58495370371</v>
+        <v>46124.33495370371</v>
       </c>
       <c r="E193">
         <v>74557</v>
@@ -30363,7 +30363,7 @@
         <v>46124.33535738426</v>
       </c>
       <c r="D194" s="1">
-        <v>46124.58530092592</v>
+        <v>46124.33530092592</v>
       </c>
       <c r="E194">
         <v>75076</v>
@@ -30506,7 +30506,7 @@
         <v>46124.33567443287</v>
       </c>
       <c r="D195" s="1">
-        <v>46124.585648148146</v>
+        <v>46124.335648148146</v>
       </c>
       <c r="E195">
         <v>75579</v>
@@ -30649,7 +30649,7 @@
         <v>46124.336051631944</v>
       </c>
       <c r="D196" s="1">
-        <v>46124.58599537037</v>
+        <v>46124.33599537037</v>
       </c>
       <c r="E196">
         <v>76061</v>
@@ -30792,7 +30792,7 @@
         <v>46124.336382395835</v>
       </c>
       <c r="D197" s="1">
-        <v>46124.58634259259</v>
+        <v>46124.33634259259</v>
       </c>
       <c r="E197">
         <v>76593</v>
@@ -30935,7 +30935,7 @@
         <v>46124.336747291665</v>
       </c>
       <c r="D198" s="1">
-        <v>46124.586689814816</v>
+        <v>46124.336689814816</v>
       </c>
       <c r="E198">
         <v>77117</v>
@@ -31078,7 +31078,7 @@
         <v>46124.337075625</v>
       </c>
       <c r="D199" s="1">
-        <v>46124.58703703704</v>
+        <v>46124.33703703704</v>
       </c>
       <c r="E199">
         <v>77647</v>
@@ -31221,7 +31221,7 @@
         <v>46124.337791018515</v>
       </c>
       <c r="D200" s="1">
-        <v>46124.58773148148</v>
+        <v>46124.33773148148</v>
       </c>
       <c r="E200">
         <v>78693</v>
@@ -31364,7 +31364,7 @@
         <v>46124.3381362037</v>
       </c>
       <c r="D201" s="1">
-        <v>46124.5880787037</v>
+        <v>46124.3380787037</v>
       </c>
       <c r="E201">
         <v>79179</v>
@@ -31507,7 +31507,7 @@
         <v>46124.338465057874</v>
       </c>
       <c r="D202" s="1">
-        <v>46124.588425925926</v>
+        <v>46124.338425925926</v>
       </c>
       <c r="E202">
         <v>79651</v>
@@ -31650,7 +31650,7 @@
         <v>46124.33883023148</v>
       </c>
       <c r="D203" s="1">
-        <v>46124.58877314815</v>
+        <v>46124.33877314815</v>
       </c>
       <c r="E203">
         <v>80134</v>
@@ -31793,7 +31793,7 @@
         <v>46124.33915866898</v>
       </c>
       <c r="D204" s="1">
-        <v>46124.58912037037</v>
+        <v>46124.33912037037</v>
       </c>
       <c r="E204">
         <v>80627</v>
@@ -31936,7 +31936,7 @@
         <v>46124.33952375</v>
       </c>
       <c r="D205" s="1">
-        <v>46124.589467592596</v>
+        <v>46124.339467592596</v>
       </c>
       <c r="E205">
         <v>81150</v>
@@ -32079,7 +32079,7 @@
         <v>46124.339853287034</v>
       </c>
       <c r="D206" s="1">
-        <v>46124.58981481481</v>
+        <v>46124.33981481481</v>
       </c>
       <c r="E206">
         <v>81665</v>
@@ -32222,7 +32222,7 @@
         <v>46124.34021991898</v>
       </c>
       <c r="D207" s="1">
-        <v>46124.590162037035</v>
+        <v>46124.340162037035</v>
       </c>
       <c r="E207">
         <v>82186</v>
@@ -32365,7 +32365,7 @@
         <v>46124.340548125</v>
       </c>
       <c r="D208" s="1">
-        <v>46124.59050925926</v>
+        <v>46124.34050925926</v>
       </c>
       <c r="E208">
         <v>82714</v>
@@ -32508,7 +32508,7 @@
         <v>46124.34091265046</v>
       </c>
       <c r="D209" s="1">
-        <v>46124.59085648148</v>
+        <v>46124.34085648148</v>
       </c>
       <c r="E209">
         <v>83211</v>
@@ -32651,7 +32651,7 @@
         <v>46124.34124368055</v>
       </c>
       <c r="D210" s="1">
-        <v>46124.591203703705</v>
+        <v>46124.341203703705</v>
       </c>
       <c r="E210">
         <v>83699</v>
@@ -32794,7 +32794,7 @@
         <v>46124.341608125</v>
       </c>
       <c r="D211" s="1">
-        <v>46124.59155092593</v>
+        <v>46124.34155092593</v>
       </c>
       <c r="E211">
         <v>84144</v>
@@ -32937,7 +32937,7 @@
         <v>46124.341936689816</v>
       </c>
       <c r="D212" s="1">
-        <v>46124.591898148145</v>
+        <v>46124.341898148145</v>
       </c>
       <c r="E212">
         <v>84600</v>
@@ -33080,7 +33080,7 @@
         <v>46124.34230710648</v>
       </c>
       <c r="D213" s="1">
-        <v>46124.59224537037</v>
+        <v>46124.34224537037</v>
       </c>
       <c r="E213">
         <v>85047</v>
@@ -33223,7 +33223,7 @@
         <v>46124.34263130787</v>
       </c>
       <c r="D214" s="1">
-        <v>46124.59259259259</v>
+        <v>46124.34259259259</v>
       </c>
       <c r="E214">
         <v>85554</v>
@@ -33366,7 +33366,7 @@
         <v>46124.342997025466</v>
       </c>
       <c r="D215" s="1">
-        <v>46124.592939814815</v>
+        <v>46124.342939814815</v>
       </c>
       <c r="E215">
         <v>86124</v>
@@ -33509,7 +33509,7 @@
         <v>46124.34332630787</v>
       </c>
       <c r="D216" s="1">
-        <v>46124.59328703704</v>
+        <v>46124.34328703704</v>
       </c>
       <c r="E216">
         <v>86776</v>
@@ -33652,7 +33652,7 @@
         <v>46124.343690636575</v>
       </c>
       <c r="D217" s="1">
-        <v>46124.59363425926</v>
+        <v>46124.34363425926</v>
       </c>
       <c r="E217">
         <v>87437</v>
@@ -33795,7 +33795,7 @@
         <v>46124.344020439814</v>
       </c>
       <c r="D218" s="1">
-        <v>46124.593981481485</v>
+        <v>46124.343981481485</v>
       </c>
       <c r="E218">
         <v>88085</v>
@@ -33938,7 +33938,7 @@
         <v>46124.344385474535</v>
       </c>
       <c r="D219" s="1">
-        <v>46124.5943287037</v>
+        <v>46124.3443287037</v>
       </c>
       <c r="E219">
         <v>88650</v>
@@ -34081,7 +34081,7 @@
         <v>46124.34470407407</v>
       </c>
       <c r="D220" s="1">
-        <v>46124.594675925924</v>
+        <v>46124.344675925924</v>
       </c>
       <c r="E220">
         <v>89129</v>
@@ -34224,7 +34224,7 @@
         <v>46124.34508107639</v>
       </c>
       <c r="D221" s="1">
-        <v>46124.59502314815</v>
+        <v>46124.34502314815</v>
       </c>
       <c r="E221">
         <v>89562</v>
@@ -34367,7 +34367,7 @@
         <v>46124.34541054398</v>
       </c>
       <c r="D222" s="1">
-        <v>46124.59537037037</v>
+        <v>46124.34537037037</v>
       </c>
       <c r="E222">
         <v>89989</v>
@@ -34510,7 +34510,7 @@
         <v>46124.345774155096</v>
       </c>
       <c r="D223" s="1">
-        <v>46124.595717592594</v>
+        <v>46124.345717592594</v>
       </c>
       <c r="E223">
         <v>90478</v>
@@ -34653,7 +34653,7 @@
         <v>46124.34610431713</v>
       </c>
       <c r="D224" s="1">
-        <v>46124.59606481482</v>
+        <v>46124.34606481482</v>
       </c>
       <c r="E224">
         <v>91027</v>
@@ -34796,7 +34796,7 @@
         <v>46124.346469317126</v>
       </c>
       <c r="D225" s="1">
-        <v>46124.59641203703</v>
+        <v>46124.34641203703</v>
       </c>
       <c r="E225">
         <v>91612</v>
@@ -35095,7 +35095,7 @@
         <v>46124.34716493056</v>
       </c>
       <c r="D2" s="1">
-        <v>46124.59710648148</v>
+        <v>46124.34710648148</v>
       </c>
       <c r="E2">
         <v>87325</v>
@@ -35202,7 +35202,7 @@
         <v>46124.3474830787</v>
       </c>
       <c r="D3" s="1">
-        <v>46124.597453703704</v>
+        <v>46124.347453703704</v>
       </c>
       <c r="E3">
         <v>84486</v>
@@ -35333,7 +35333,7 @@
         <v>46124.34785737268</v>
       </c>
       <c r="D4" s="1">
-        <v>46124.59780092593</v>
+        <v>46124.34780092593</v>
       </c>
       <c r="E4">
         <v>81809</v>
@@ -35476,7 +35476,7 @@
         <v>46124.34832587963</v>
       </c>
       <c r="D5" s="1">
-        <v>46124.59814814815</v>
+        <v>46124.34814814815</v>
       </c>
       <c r="E5">
         <v>79339</v>
@@ -35619,7 +35619,7 @@
         <v>46124.34855224537</v>
       </c>
       <c r="D6" s="1">
-        <v>46124.598495370374</v>
+        <v>46124.348495370374</v>
       </c>
       <c r="E6">
         <v>76994</v>
@@ -35762,7 +35762,7 @@
         <v>46124.348869884256</v>
       </c>
       <c r="D7" s="1">
-        <v>46124.59884259259</v>
+        <v>46124.34884259259</v>
       </c>
       <c r="E7">
         <v>74768</v>
@@ -35905,7 +35905,7 @@
         <v>46124.34924643519</v>
       </c>
       <c r="D8" s="1">
-        <v>46124.59918981481</v>
+        <v>46124.34918981481</v>
       </c>
       <c r="E8">
         <v>72696</v>
@@ -36048,7 +36048,7 @@
         <v>46124.34956469907</v>
       </c>
       <c r="D9" s="1">
-        <v>46124.59953703704</v>
+        <v>46124.34953703704</v>
       </c>
       <c r="E9">
         <v>70632</v>
@@ -36191,7 +36191,7 @@
         <v>46124.34994146991</v>
       </c>
       <c r="D10" s="1">
-        <v>46124.59988425926</v>
+        <v>46124.34988425926</v>
       </c>
       <c r="E10">
         <v>68700</v>
@@ -36334,7 +36334,7 @@
         <v>46124.35025957176</v>
       </c>
       <c r="D11" s="1">
-        <v>46124.60023148148</v>
+        <v>46124.35023148148</v>
       </c>
       <c r="E11">
         <v>66883</v>
@@ -36477,7 +36477,7 @@
         <v>46124.350966956015</v>
       </c>
       <c r="D12" s="1">
-        <v>46124.60092592592</v>
+        <v>46124.35092592592</v>
       </c>
       <c r="E12">
         <v>63456</v>
@@ -36620,7 +36620,7 @@
         <v>46124.35133087963</v>
       </c>
       <c r="D13" s="1">
-        <v>46124.601273148146</v>
+        <v>46124.351273148146</v>
       </c>
       <c r="E13">
         <v>61837</v>
@@ -36763,7 +36763,7 @@
         <v>46124.35166013889</v>
       </c>
       <c r="D14" s="1">
-        <v>46124.60162037037</v>
+        <v>46124.35162037037</v>
       </c>
       <c r="E14">
         <v>60309</v>
@@ -36906,7 +36906,7 @@
         <v>46124.35202474537</v>
       </c>
       <c r="D15" s="1">
-        <v>46124.60196759259</v>
+        <v>46124.35196759259</v>
       </c>
       <c r="E15">
         <v>58804</v>
@@ -37049,7 +37049,7 @@
         <v>46124.3523547338</v>
       </c>
       <c r="D16" s="1">
-        <v>46124.602314814816</v>
+        <v>46124.352314814816</v>
       </c>
       <c r="E16">
         <v>57308</v>
@@ -37192,7 +37192,7 @@
         <v>46124.35272296296</v>
       </c>
       <c r="D17" s="1">
-        <v>46124.60266203704</v>
+        <v>46124.35266203704</v>
       </c>
       <c r="E17">
         <v>55871</v>
@@ -37335,7 +37335,7 @@
         <v>46124.35304854166</v>
       </c>
       <c r="D18" s="1">
-        <v>46124.60300925926</v>
+        <v>46124.35300925926</v>
       </c>
       <c r="E18">
         <v>54556</v>
@@ -37478,7 +37478,7 @@
         <v>46124.35341321759</v>
       </c>
       <c r="D19" s="1">
-        <v>46124.60335648148</v>
+        <v>46124.35335648148</v>
       </c>
       <c r="E19">
         <v>53292</v>
@@ -37621,7 +37621,7 @@
         <v>46124.35373138889</v>
       </c>
       <c r="D20" s="1">
-        <v>46124.6037037037</v>
+        <v>46124.3537037037</v>
       </c>
       <c r="E20">
         <v>52090</v>
@@ -37764,7 +37764,7 @@
         <v>46124.354108252315</v>
       </c>
       <c r="D21" s="1">
-        <v>46124.604050925926</v>
+        <v>46124.354050925926</v>
       </c>
       <c r="E21">
         <v>50982</v>
@@ -37907,7 +37907,7 @@
         <v>46124.354426412036</v>
       </c>
       <c r="D22" s="1">
-        <v>46124.60439814815</v>
+        <v>46124.35439814815</v>
       </c>
       <c r="E22">
         <v>49936</v>
@@ -38050,7 +38050,7 @@
         <v>46124.35480512732</v>
       </c>
       <c r="D23" s="1">
-        <v>46124.60474537037</v>
+        <v>46124.35474537037</v>
       </c>
       <c r="E23">
         <v>48914</v>
@@ -38193,7 +38193,7 @@
         <v>46124.355120775464</v>
       </c>
       <c r="D24" s="1">
-        <v>46124.605092592596</v>
+        <v>46124.355092592596</v>
       </c>
       <c r="E24">
         <v>47848</v>
@@ -38336,7 +38336,7 @@
         <v>46124.35550222222</v>
       </c>
       <c r="D25" s="1">
-        <v>46124.60543981481</v>
+        <v>46124.35543981481</v>
       </c>
       <c r="E25">
         <v>46771</v>
@@ -38479,7 +38479,7 @@
         <v>46124.35581527778</v>
       </c>
       <c r="D26" s="1">
-        <v>46124.605787037035</v>
+        <v>46124.355787037035</v>
       </c>
       <c r="E26">
         <v>45714</v>
@@ -38622,7 +38622,7 @@
         <v>46124.356197430556</v>
       </c>
       <c r="D27" s="1">
-        <v>46124.60613425926</v>
+        <v>46124.35613425926</v>
       </c>
       <c r="E27">
         <v>44653</v>
@@ -38765,7 +38765,7 @@
         <v>46124.35650954861</v>
       </c>
       <c r="D28" s="1">
-        <v>46124.60648148148</v>
+        <v>46124.35648148148</v>
       </c>
       <c r="E28">
         <v>43634</v>
@@ -38908,7 +38908,7 @@
         <v>46124.356886030095</v>
       </c>
       <c r="D29" s="1">
-        <v>46124.606828703705</v>
+        <v>46124.356828703705</v>
       </c>
       <c r="E29">
         <v>42666</v>
@@ -39051,7 +39051,7 @@
         <v>46124.35720413194</v>
       </c>
       <c r="D30" s="1">
-        <v>46124.60717592593</v>
+        <v>46124.35717592593</v>
       </c>
       <c r="E30">
         <v>41717</v>
@@ -39194,7 +39194,7 @@
         <v>46124.35790065972</v>
       </c>
       <c r="D31" s="1">
-        <v>46124.60787037037</v>
+        <v>46124.35787037037</v>
       </c>
       <c r="E31">
         <v>39891</v>
@@ -39337,7 +39337,7 @@
         <v>46124.35827502315</v>
       </c>
       <c r="D32" s="1">
-        <v>46124.60821759259</v>
+        <v>46124.35821759259</v>
       </c>
       <c r="E32">
         <v>39079</v>
@@ -39480,7 +39480,7 @@
         <v>46124.3586059375</v>
       </c>
       <c r="D33" s="1">
-        <v>46124.608564814815</v>
+        <v>46124.358564814815</v>
       </c>
       <c r="E33">
         <v>38259</v>
@@ -39623,7 +39623,7 @@
         <v>46124.35897030093</v>
       </c>
       <c r="D34" s="1">
-        <v>46124.60891203704</v>
+        <v>46124.35891203704</v>
       </c>
       <c r="E34">
         <v>37436</v>
@@ -39766,7 +39766,7 @@
         <v>46124.359288900465</v>
       </c>
       <c r="D35" s="1">
-        <v>46124.60925925926</v>
+        <v>46124.35925925926</v>
       </c>
       <c r="E35">
         <v>36596</v>
@@ -39909,7 +39909,7 @@
         <v>46124.35999427083</v>
       </c>
       <c r="D36" s="1">
-        <v>46124.6099537037</v>
+        <v>46124.3599537037</v>
       </c>
       <c r="E36">
         <v>34943</v>
@@ -40052,7 +40052,7 @@
         <v>46124.3606891088</v>
       </c>
       <c r="D37" s="1">
-        <v>46124.61064814815</v>
+        <v>46124.36064814815</v>
       </c>
       <c r="E37">
         <v>33337</v>
@@ -40195,7 +40195,7 @@
         <v>46124.3610605787</v>
       </c>
       <c r="D38" s="1">
-        <v>46124.61099537037</v>
+        <v>46124.36099537037</v>
       </c>
       <c r="E38">
         <v>32575</v>
@@ -40338,7 +40338,7 @@
         <v>46124.361371122686</v>
       </c>
       <c r="D39" s="1">
-        <v>46124.611342592594</v>
+        <v>46124.361342592594</v>
       </c>
       <c r="E39">
         <v>31829</v>
@@ -40481,7 +40481,7 @@
         <v>46124.361754467594</v>
       </c>
       <c r="D40" s="1">
-        <v>46124.61168981482</v>
+        <v>46124.36168981482</v>
       </c>
       <c r="E40">
         <v>31091</v>
@@ -40624,7 +40624,7 @@
         <v>46124.36207778935</v>
       </c>
       <c r="D41" s="1">
-        <v>46124.61203703703</v>
+        <v>46124.36203703703</v>
       </c>
       <c r="E41">
         <v>30368</v>
@@ -40767,7 +40767,7 @@
         <v>46124.36245039352</v>
       </c>
       <c r="D42" s="1">
-        <v>46124.61238425926</v>
+        <v>46124.36238425926</v>
       </c>
       <c r="E42">
         <v>29641</v>
@@ -40910,7 +40910,7 @@
         <v>46124.362760752316</v>
       </c>
       <c r="D43" s="1">
-        <v>46124.61273148148</v>
+        <v>46124.36273148148</v>
       </c>
       <c r="E43">
         <v>28923</v>
@@ -41053,7 +41053,7 @@
         <v>46124.36314383102</v>
       </c>
       <c r="D44" s="1">
-        <v>46124.613078703704</v>
+        <v>46124.363078703704</v>
       </c>
       <c r="E44">
         <v>28190</v>
@@ -41196,7 +41196,7 @@
         <v>46124.3634546875</v>
       </c>
       <c r="D45" s="1">
-        <v>46124.61342592593</v>
+        <v>46124.36342592593</v>
       </c>
       <c r="E45">
         <v>27456</v>
@@ -41339,7 +41339,7 @@
         <v>46124.36414949074</v>
       </c>
       <c r="D46" s="1">
-        <v>46124.614120370374</v>
+        <v>46124.364120370374</v>
       </c>
       <c r="E46">
         <v>26037</v>
@@ -41482,7 +41482,7 @@
         <v>46124.364533761574</v>
       </c>
       <c r="D47" s="1">
-        <v>46124.61446759259</v>
+        <v>46124.36446759259</v>
       </c>
       <c r="E47">
         <v>25348</v>
@@ -41625,7 +41625,7 @@
         <v>46124.364856319444</v>
       </c>
       <c r="D48" s="1">
-        <v>46124.61481481481</v>
+        <v>46124.36481481481</v>
       </c>
       <c r="E48">
         <v>24682</v>
@@ -41768,7 +41768,7 @@
         <v>46124.36522042824</v>
       </c>
       <c r="D49" s="1">
-        <v>46124.61516203704</v>
+        <v>46124.36516203704</v>
       </c>
       <c r="E49">
         <v>24013</v>
@@ -41911,7 +41911,7 @@
         <v>46124.36553790509</v>
       </c>
       <c r="D50" s="1">
-        <v>46124.61550925926</v>
+        <v>46124.36550925926</v>
       </c>
       <c r="E50">
         <v>23349</v>
@@ -42054,7 +42054,7 @@
         <v>46124.36623344907</v>
       </c>
       <c r="D51" s="1">
-        <v>46124.61620370371</v>
+        <v>46124.36620370371</v>
       </c>
       <c r="E51">
         <v>22010</v>
@@ -42197,7 +42197,7 @@
         <v>46124.36661</v>
       </c>
       <c r="D52" s="1">
-        <v>46124.61655092592</v>
+        <v>46124.36655092592</v>
       </c>
       <c r="E52">
         <v>21363</v>
@@ -42340,7 +42340,7 @@
         <v>46124.36692665509</v>
       </c>
       <c r="D53" s="1">
-        <v>46124.616898148146</v>
+        <v>46124.366898148146</v>
       </c>
       <c r="E53">
         <v>20749</v>
@@ -42483,7 +42483,7 @@
         <v>46124.367304976855</v>
       </c>
       <c r="D54" s="1">
-        <v>46124.61724537037</v>
+        <v>46124.36724537037</v>
       </c>
       <c r="E54">
         <v>20131</v>
@@ -42626,7 +42626,7 @@
         <v>46124.36763424768</v>
       </c>
       <c r="D55" s="1">
-        <v>46124.61759259259</v>
+        <v>46124.36759259259</v>
       </c>
       <c r="E55">
         <v>19503</v>
@@ -42769,7 +42769,7 @@
         <v>46124.36799918982</v>
       </c>
       <c r="D56" s="1">
-        <v>46124.617939814816</v>
+        <v>46124.367939814816</v>
       </c>
       <c r="E56">
         <v>18892</v>
@@ -42912,7 +42912,7 @@
         <v>46124.368318981484</v>
       </c>
       <c r="D57" s="1">
-        <v>46124.61828703704</v>
+        <v>46124.36828703704</v>
       </c>
       <c r="E57">
         <v>18282</v>
@@ -43055,7 +43055,7 @@
         <v>46124.36869217593</v>
       </c>
       <c r="D58" s="1">
-        <v>46124.61863425926</v>
+        <v>46124.36863425926</v>
       </c>
       <c r="E58">
         <v>17681</v>
@@ -43198,7 +43198,7 @@
         <v>46124.36901048611</v>
       </c>
       <c r="D59" s="1">
-        <v>46124.61898148148</v>
+        <v>46124.36898148148</v>
       </c>
       <c r="E59">
         <v>17104</v>
@@ -43341,7 +43341,7 @@
         <v>46124.36938628472</v>
       </c>
       <c r="D60" s="1">
-        <v>46124.6193287037</v>
+        <v>46124.3693287037</v>
       </c>
       <c r="E60">
         <v>16556</v>
@@ -43484,7 +43484,7 @@
         <v>46124.369705543984</v>
       </c>
       <c r="D61" s="1">
-        <v>46124.619675925926</v>
+        <v>46124.369675925926</v>
       </c>
       <c r="E61">
         <v>16009</v>
@@ -43627,7 +43627,7 @@
         <v>46124.37008108796</v>
       </c>
       <c r="D62" s="1">
-        <v>46124.62002314815</v>
+        <v>46124.37002314815</v>
       </c>
       <c r="E62">
         <v>15499</v>
@@ -43770,7 +43770,7 @@
         <v>46124.37039950232</v>
       </c>
       <c r="D63" s="1">
-        <v>46124.62037037037</v>
+        <v>46124.37037037037</v>
       </c>
       <c r="E63">
         <v>14999</v>
@@ -43913,7 +43913,7 @@
         <v>46124.3707756713</v>
       </c>
       <c r="D64" s="1">
-        <v>46124.620717592596</v>
+        <v>46124.370717592596</v>
       </c>
       <c r="E64">
         <v>14531</v>
@@ -44056,7 +44056,7 @@
         <v>46124.37109390046</v>
       </c>
       <c r="D65" s="1">
-        <v>46124.62106481481</v>
+        <v>46124.37106481481</v>
       </c>
       <c r="E65">
         <v>14047</v>
@@ -44199,7 +44199,7 @@
         <v>46124.37147104167</v>
       </c>
       <c r="D66" s="1">
-        <v>46124.621412037035</v>
+        <v>46124.371412037035</v>
       </c>
       <c r="E66">
         <v>13517</v>
@@ -44342,7 +44342,7 @@
         <v>46124.37180836806</v>
       </c>
       <c r="D67" s="1">
-        <v>46124.62175925926</v>
+        <v>46124.37175925926</v>
       </c>
       <c r="E67">
         <v>12972</v>
@@ -44485,7 +44485,7 @@
         <v>46124.37216575231</v>
       </c>
       <c r="D68" s="1">
-        <v>46124.62210648148</v>
+        <v>46124.37210648148</v>
       </c>
       <c r="E68">
         <v>12438</v>
@@ -44628,7 +44628,7 @@
         <v>46124.372482708335</v>
       </c>
       <c r="D69" s="1">
-        <v>46124.622453703705</v>
+        <v>46124.372453703705</v>
       </c>
       <c r="E69">
         <v>11915</v>
@@ -44771,7 +44771,7 @@
         <v>46124.37286019676</v>
       </c>
       <c r="D70" s="1">
-        <v>46124.62280092593</v>
+        <v>46124.37280092593</v>
       </c>
       <c r="E70">
         <v>11387</v>
@@ -44914,7 +44914,7 @@
         <v>46124.373177824076</v>
       </c>
       <c r="D71" s="1">
-        <v>46124.623148148145</v>
+        <v>46124.373148148145</v>
       </c>
       <c r="E71">
         <v>10855</v>
@@ -45057,7 +45057,7 @@
         <v>46124.37355510417</v>
       </c>
       <c r="D72" s="1">
-        <v>46124.62349537037</v>
+        <v>46124.37349537037</v>
       </c>
       <c r="E72">
         <v>10341</v>
@@ -45200,7 +45200,7 @@
         <v>46124.373871828706</v>
       </c>
       <c r="D73" s="1">
-        <v>46124.62384259259</v>
+        <v>46124.37384259259</v>
       </c>
       <c r="E73">
         <v>9851</v>
@@ -45343,7 +45343,7 @@
         <v>46124.37424806713</v>
       </c>
       <c r="D74" s="1">
-        <v>46124.624189814815</v>
+        <v>46124.374189814815</v>
       </c>
       <c r="E74">
         <v>9380</v>
@@ -45486,7 +45486,7 @@
         <v>46124.3752684838</v>
       </c>
       <c r="D75" s="1">
-        <v>46124.625231481485</v>
+        <v>46124.375231481485</v>
       </c>
       <c r="E75">
         <v>7994</v>
@@ -45629,7 +45629,7 @@
         <v>46124.37563934028</v>
       </c>
       <c r="D76" s="1">
-        <v>46124.6255787037</v>
+        <v>46124.3755787037</v>
       </c>
       <c r="E76">
         <v>7544</v>
@@ -45772,7 +45772,7 @@
         <v>46124.37596377315</v>
       </c>
       <c r="D77" s="1">
-        <v>46124.625925925924</v>
+        <v>46124.375925925924</v>
       </c>
       <c r="E77">
         <v>7072</v>
@@ -45915,7 +45915,7 @@
         <v>46124.37668166667</v>
       </c>
       <c r="D78" s="1">
-        <v>46124.62662037037</v>
+        <v>46124.37662037037</v>
       </c>
       <c r="E78">
         <v>6126</v>
@@ -46058,7 +46058,7 @@
         <v>46124.381938680555</v>
       </c>
       <c r="D79" s="1">
-        <v>46124.63182870371</v>
+        <v>46124.38182870371</v>
       </c>
       <c r="E79">
         <v>4595</v>
